--- a/files/ps2/starter.xlsx
+++ b/files/ps2/starter.xlsx
@@ -16,13 +16,6 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Benchmarks" sheetId="7" state="visible" r:id="rId7"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Checks" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
-  <definedNames>
-    <definedName name="CHK1">'Checks'!$C$4</definedName>
-    <definedName name="CHK2">'Checks'!$C$5</definedName>
-    <definedName name="CHK3">'Checks'!$C$6</definedName>
-    <definedName name="CHK4">'Checks'!$C$7</definedName>
-    <definedName name="CHK5">'Checks'!$C$8</definedName>
-  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -763,7 +756,6 @@
       </c>
       <c r="C15" s="2">
         <f> 0.08 × 12 × $2,500; expensed at signing, PAID quarterly (Mar/Jun/Sep/Dec)</f>
-        <v/>
       </c>
     </row>
     <row r="16">
@@ -777,7 +769,6 @@
       </c>
       <c r="C16" s="2">
         <f> 12 × $2,500 × 0.90; collected in the signing month</f>
-        <v/>
       </c>
     </row>
     <row r="17">
@@ -1427,7 +1418,6 @@
       </c>
       <c r="B6" s="18">
         <f>B3+B4-B5</f>
-        <v/>
       </c>
     </row>
     <row r="8">
@@ -1473,7 +1463,6 @@
       </c>
       <c r="B14" s="19">
         <f>B12+B13</f>
-        <v/>
       </c>
     </row>
     <row r="16" ht="28" customHeight="1">
@@ -1636,51 +1625,39 @@
       </c>
       <c r="B4" s="18">
         <f>Assumptions!B29</f>
-        <v/>
       </c>
       <c r="C4" s="18">
         <f>B3</f>
-        <v/>
       </c>
       <c r="D4" s="18">
         <f>C3</f>
-        <v/>
       </c>
       <c r="E4" s="18">
         <f>D3</f>
-        <v/>
       </c>
       <c r="F4" s="18">
         <f>E3</f>
-        <v/>
       </c>
       <c r="G4" s="18">
         <f>F3</f>
-        <v/>
       </c>
       <c r="H4" s="18">
         <f>G3</f>
-        <v/>
       </c>
       <c r="I4" s="18">
         <f>H3</f>
-        <v/>
       </c>
       <c r="J4" s="18">
         <f>I3</f>
-        <v/>
       </c>
       <c r="K4" s="18">
         <f>J3</f>
-        <v/>
       </c>
       <c r="L4" s="18">
         <f>K3</f>
-        <v/>
       </c>
       <c r="M4" s="18">
         <f>L3</f>
-        <v/>
       </c>
     </row>
     <row r="5">
@@ -1691,47 +1668,36 @@
       </c>
       <c r="B5" s="18">
         <f>'Customer &amp; Revenue'!C6</f>
-        <v/>
       </c>
       <c r="C5" s="18">
         <f>'Customer &amp; Revenue'!D6</f>
-        <v/>
       </c>
       <c r="D5" s="18">
         <f>'Customer &amp; Revenue'!E6</f>
-        <v/>
       </c>
       <c r="E5" s="18">
         <f>'Customer &amp; Revenue'!F6</f>
-        <v/>
       </c>
       <c r="F5" s="18">
         <f>'Customer &amp; Revenue'!G6</f>
-        <v/>
       </c>
       <c r="G5" s="18">
         <f>'Customer &amp; Revenue'!H6</f>
-        <v/>
       </c>
       <c r="H5" s="18">
         <f>'Customer &amp; Revenue'!I6</f>
-        <v/>
       </c>
       <c r="I5" s="18">
         <f>'Customer &amp; Revenue'!J6</f>
-        <v/>
       </c>
       <c r="J5" s="18">
         <f>'Customer &amp; Revenue'!K6</f>
-        <v/>
       </c>
       <c r="K5" s="18">
         <f>'Customer &amp; Revenue'!L6</f>
-        <v/>
       </c>
       <c r="L5" s="18">
         <f>'Customer &amp; Revenue'!M6</f>
-        <v/>
       </c>
       <c r="M5" s="18" t="n"/>
     </row>
@@ -1743,27 +1709,21 @@
       </c>
       <c r="B6" s="18">
         <f>ROUNDUP(B5/15,0)</f>
-        <v/>
       </c>
       <c r="C6" s="18">
         <f>ROUNDUP(C5/15,0)</f>
-        <v/>
       </c>
       <c r="D6" s="18">
         <f>ROUNDUP(D5/15,0)</f>
-        <v/>
       </c>
       <c r="E6" s="18">
         <f>ROUNDUP(E5/15,0)</f>
-        <v/>
       </c>
       <c r="F6" s="18">
         <f>ROUNDUP(F5/15,0)</f>
-        <v/>
       </c>
       <c r="G6" s="18">
         <f>ROUNDUP(G5/15,0)</f>
-        <v/>
       </c>
       <c r="H6" s="18" t="n">
         <v>10</v>
@@ -1835,51 +1795,39 @@
       </c>
       <c r="B8" s="20">
         <f>B7*0.6</f>
-        <v/>
       </c>
       <c r="C8" s="20">
         <f>C7*0.6</f>
-        <v/>
       </c>
       <c r="D8" s="20">
         <f>D7*0.6</f>
-        <v/>
       </c>
       <c r="E8" s="20">
         <f>E7*0.6</f>
-        <v/>
       </c>
       <c r="F8" s="20">
         <f>F7*0.6</f>
-        <v/>
       </c>
       <c r="G8" s="20">
         <f>G7*0.6</f>
-        <v/>
       </c>
       <c r="H8" s="20">
         <f>H7*0.6</f>
-        <v/>
       </c>
       <c r="I8" s="20">
         <f>I7*0.6</f>
-        <v/>
       </c>
       <c r="J8" s="20">
         <f>J7*0.6</f>
-        <v/>
       </c>
       <c r="K8" s="20">
         <f>K7*0.6</f>
-        <v/>
       </c>
       <c r="L8" s="20">
         <f>L7*0.6</f>
-        <v/>
       </c>
       <c r="M8" s="20">
         <f>M7*0.6</f>
-        <v/>
       </c>
     </row>
     <row r="9">
@@ -1890,51 +1838,39 @@
       </c>
       <c r="B9" s="20">
         <f>B7*0.4</f>
-        <v/>
       </c>
       <c r="C9" s="20">
         <f>C7*0.4</f>
-        <v/>
       </c>
       <c r="D9" s="20">
         <f>D7*0.4</f>
-        <v/>
       </c>
       <c r="E9" s="20">
         <f>E7*0.4</f>
-        <v/>
       </c>
       <c r="F9" s="20">
         <f>F7*0.4</f>
-        <v/>
       </c>
       <c r="G9" s="20">
         <f>G7*0.4</f>
-        <v/>
       </c>
       <c r="H9" s="20">
         <f>H7*0.4</f>
-        <v/>
       </c>
       <c r="I9" s="20">
         <f>I7*0.4</f>
-        <v/>
       </c>
       <c r="J9" s="20">
         <f>J7*0.4</f>
-        <v/>
       </c>
       <c r="K9" s="20">
         <f>K7*0.4</f>
-        <v/>
       </c>
       <c r="L9" s="20">
         <f>L7*0.4</f>
-        <v/>
       </c>
       <c r="M9" s="20">
         <f>M7*0.4</f>
-        <v/>
       </c>
     </row>
     <row r="10">
@@ -1988,51 +1924,39 @@
       </c>
       <c r="B11" s="21">
         <f>B3+B6+B7+B10</f>
-        <v/>
       </c>
       <c r="C11" s="21">
         <f>C3+C6+C7+C10</f>
-        <v/>
       </c>
       <c r="D11" s="21">
         <f>D3+D6+D7+D10</f>
-        <v/>
       </c>
       <c r="E11" s="21">
         <f>E3+E6+E7+E10</f>
-        <v/>
       </c>
       <c r="F11" s="21">
         <f>F3+F6+F7+F10</f>
-        <v/>
       </c>
       <c r="G11" s="21">
         <f>G3+G6+G7+G10</f>
-        <v/>
       </c>
       <c r="H11" s="21">
         <f>H3+H6+H7+H10</f>
-        <v/>
       </c>
       <c r="I11" s="21">
         <f>I3+I6+I7+I10</f>
-        <v/>
       </c>
       <c r="J11" s="21">
         <f>J3+J6+J7+J10</f>
-        <v/>
       </c>
       <c r="K11" s="21">
         <f>K3+K6+K7+K10</f>
-        <v/>
       </c>
       <c r="L11" s="21">
         <f>L3+L6+L7+L10</f>
-        <v/>
       </c>
       <c r="M11" s="21">
         <f>M3+M6+M7+M10</f>
-        <v/>
       </c>
     </row>
     <row r="13" ht="30" customHeight="1">
@@ -3175,7 +3099,6 @@
       </c>
       <c r="C4" s="25">
         <f>'Customer &amp; Revenue'!M6</f>
-        <v/>
       </c>
     </row>
     <row r="5">
@@ -3191,7 +3114,6 @@
       </c>
       <c r="C5" s="26">
         <f>SUM('Income Statement'!B5:M5)</f>
-        <v/>
       </c>
     </row>
     <row r="6">
@@ -3207,7 +3129,6 @@
       </c>
       <c r="C6" s="25">
         <f>'Headcount'!M11</f>
-        <v/>
       </c>
     </row>
     <row r="7">
@@ -3223,7 +3144,6 @@
       </c>
       <c r="C7" s="26">
         <f>'Deferred Revenue'!M6</f>
-        <v/>
       </c>
     </row>
     <row r="8">
@@ -3239,7 +3159,6 @@
       </c>
       <c r="C8" s="26">
         <f>'Cash Walk'!M18</f>
-        <v/>
       </c>
     </row>
   </sheetData>
